--- a/data/trans_camb/IP08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,92</t>
+          <t>-2,44; 8,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,9</t>
+          <t>-5,94; 3,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,78</t>
+          <t>-2,33; 9,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 6,36</t>
+          <t>-6,05; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 0,54</t>
+          <t>-10,22; 0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 28,98</t>
+          <t>-3,65; 27,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,89</t>
+          <t>-2,82; 5,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 1,02</t>
+          <t>-6,73; 0,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 16,67</t>
+          <t>-1,09; 17,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 196,32</t>
+          <t>-31,9; 195,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 88,46</t>
+          <t>-64,87; 83,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 185,39</t>
+          <t>-27,97; 205,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 75,69</t>
+          <t>-43,79; 73,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 11,38</t>
+          <t>-73,52; 3,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 354,45</t>
+          <t>-31,38; 296,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 82,23</t>
+          <t>-26,71; 78,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 15,44</t>
+          <t>-60,03; 9,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 217,93</t>
+          <t>-12,5; 222,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,26</t>
+          <t>0,56; 10,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,59</t>
+          <t>-2,94; 5,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,86</t>
+          <t>-1,7; 12,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,51</t>
+          <t>-4,05; 6,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 0,48</t>
+          <t>-8,99; 1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 2,09</t>
+          <t>-7,73; 2,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,9</t>
+          <t>-0,77; 6,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,72</t>
+          <t>-4,61; 1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,55</t>
+          <t>-3,74; 4,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 178,56</t>
+          <t>4,31; 166,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 96,28</t>
+          <t>-29,57; 94,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 222,73</t>
+          <t>-20,41; 189,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 62,72</t>
+          <t>-26,75; 67,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 5,0</t>
+          <t>-57,43; 11,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 21,37</t>
+          <t>-49,73; 19,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 78,54</t>
+          <t>-7,33; 71,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 19,63</t>
+          <t>-37,27; 19,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 53,18</t>
+          <t>-30,95; 48,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,81</t>
+          <t>2,03; 12,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,94</t>
+          <t>-3,24; 4,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,85</t>
+          <t>-3,26; 7,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 11,36</t>
+          <t>-0,81; 11,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -0,29</t>
+          <t>-9,6; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 7,33</t>
+          <t>-5,11; 7,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,76</t>
+          <t>2,0; 10,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,29</t>
+          <t>-5,7; 0,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,58</t>
+          <t>-2,86; 5,4</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,04; 343,13</t>
+          <t>22,57; 352,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 131,21</t>
+          <t>-47,21; 145,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 184,66</t>
+          <t>-42,84; 180,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 161,37</t>
+          <t>-9,52; 145,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,32; -2,07</t>
+          <t>-73,44; 5,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 94,62</t>
+          <t>-38,19; 91,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,03; 164,59</t>
+          <t>16,85; 153,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 23,25</t>
+          <t>-55,01; 12,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 90,44</t>
+          <t>-30,1; 80,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 4,09</t>
+          <t>-5,86; 5,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -1,85</t>
+          <t>-11,47; -1,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 3,68</t>
+          <t>-7,09; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,89</t>
+          <t>-2,65; 8,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,04</t>
+          <t>-9,14; -0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 11,33</t>
+          <t>-0,86; 11,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,24</t>
+          <t>-3,18; 4,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; -2,24</t>
+          <t>-8,24; -2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,12</t>
+          <t>-2,49; 6,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 47,65</t>
+          <t>-43,92; 66,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,72; -16,12</t>
+          <t>-78,76; -14,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 44,42</t>
+          <t>-52,89; 41,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 98,05</t>
+          <t>-20,66; 104,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 2,25</t>
+          <t>-68,92; -3,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 136,92</t>
+          <t>-7,17; 136,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,4; 46,53</t>
+          <t>-25,21; 50,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,83; -23,52</t>
+          <t>-66,87; -23,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 68,98</t>
+          <t>-20,06; 64,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,9</t>
+          <t>0,93; 6,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,7</t>
+          <t>-3,62; 0,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,45</t>
+          <t>-1,48; 4,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,83</t>
+          <t>-0,76; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,31</t>
+          <t>-7,1; -2,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,05</t>
+          <t>-1,39; 5,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,58</t>
+          <t>0,74; 4,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -1,51</t>
+          <t>-4,89; -1,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,08</t>
+          <t>-0,72; 4,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,67; 84,63</t>
+          <t>9,58; 87,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 10,26</t>
+          <t>-39,5; 9,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 63,12</t>
+          <t>-16,58; 67,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 46,35</t>
+          <t>-5,06; 48,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -21,96</t>
+          <t>-54,14; -21,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 59,46</t>
+          <t>-11,42; 59,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,16; 50,84</t>
+          <t>6,88; 50,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -16,51</t>
+          <t>-44,57; -15,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 43,31</t>
+          <t>-7,46; 45,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,95</t>
+          <t>-2,85; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 3,5</t>
+          <t>-6,27; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 9,59</t>
+          <t>-2,61; 9,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 6,06</t>
+          <t>-5,93; 6,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 0,35</t>
+          <t>-10,41; 0,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 27,18</t>
+          <t>-4,2; 26,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 5,88</t>
+          <t>-2,48; 5,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,63</t>
+          <t>-6,28; 1,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 17,09</t>
+          <t>-1,08; 20,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 195,68</t>
+          <t>-28,78; 192,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 83,78</t>
+          <t>-65,34; 96,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 205,09</t>
+          <t>-29,96; 206,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 73,53</t>
+          <t>-41,23; 76,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,52; 3,78</t>
+          <t>-69,29; 9,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 296,4</t>
+          <t>-36,59; 265,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 78,76</t>
+          <t>-23,38; 77,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 9,93</t>
+          <t>-56,68; 16,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 222,61</t>
+          <t>-12,55; 264,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 10,03</t>
+          <t>1,11; 10,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,69</t>
+          <t>-2,89; 5,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 12,73</t>
+          <t>-1,79; 12,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 6,5</t>
+          <t>-4,74; 5,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,16</t>
+          <t>-9,22; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,01</t>
+          <t>-8,21; 1,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 6,49</t>
+          <t>-0,76; 6,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,85</t>
+          <t>-4,77; 1,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,66</t>
+          <t>-3,74; 4,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 166,05</t>
+          <t>8,23; 160,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 94,14</t>
+          <t>-29,63; 97,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 189,21</t>
+          <t>-21,27; 197,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 67,07</t>
+          <t>-30,62; 46,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 11,31</t>
+          <t>-57,43; 9,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 19,29</t>
+          <t>-49,97; 21,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 71,36</t>
+          <t>-6,07; 73,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 19,82</t>
+          <t>-39,52; 21,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 48,43</t>
+          <t>-30,57; 52,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,42</t>
+          <t>2,31; 12,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,81</t>
+          <t>-4,09; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 7,15</t>
+          <t>-3,12; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 11,15</t>
+          <t>-1,03; 10,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 0,13</t>
+          <t>-9,8; -0,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 7,04</t>
+          <t>-4,28; 8,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,17</t>
+          <t>2,15; 10,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,67</t>
+          <t>-5,46; 0,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,4</t>
+          <t>-2,54; 5,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,57; 352,54</t>
+          <t>25,7; 341,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 145,75</t>
+          <t>-50,83; 127,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 180,51</t>
+          <t>-40,38; 173,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 145,76</t>
+          <t>-10,1; 144,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 5,51</t>
+          <t>-73,09; 4,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 91,17</t>
+          <t>-34,64; 95,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,85; 153,13</t>
+          <t>20,63; 160,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 12,2</t>
+          <t>-55,85; 15,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 80,91</t>
+          <t>-26,28; 87,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,15</t>
+          <t>-6,01; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -1,99</t>
+          <t>-10,39; -1,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 3,48</t>
+          <t>-6,64; 3,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,71</t>
+          <t>-2,54; 7,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -0,38</t>
+          <t>-9,14; -0,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 11,35</t>
+          <t>-0,82; 11,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,46</t>
+          <t>-2,51; 5,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -2,28</t>
+          <t>-8,12; -2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,0</t>
+          <t>-2,33; 6,02</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 66,78</t>
+          <t>-44,32; 53,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,76; -14,28</t>
+          <t>-75,96; -15,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 41,8</t>
+          <t>-49,69; 45,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 104,55</t>
+          <t>-20,94; 95,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,92; -3,98</t>
+          <t>-68,57; 1,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 136,15</t>
+          <t>-9,35; 131,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 50,96</t>
+          <t>-21,04; 56,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,87; -23,44</t>
+          <t>-66,54; -24,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 64,06</t>
+          <t>-19,32; 66,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,05</t>
+          <t>0,9; 6,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,66</t>
+          <t>-3,91; 0,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,77</t>
+          <t>-1,19; 4,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,0</t>
+          <t>-0,64; 4,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -2,24</t>
+          <t>-7,08; -2,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,94</t>
+          <t>-1,62; 6,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,53</t>
+          <t>0,69; 4,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,46</t>
+          <t>-4,79; -1,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,53</t>
+          <t>-0,62; 4,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,58; 87,15</t>
+          <t>9,76; 87,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 9,05</t>
+          <t>-40,35; 14,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 67,62</t>
+          <t>-13,79; 67,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 48,68</t>
+          <t>-5,96; 47,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -21,59</t>
+          <t>-54,82; -20,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 59,36</t>
+          <t>-13,35; 61,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,88; 50,18</t>
+          <t>6,14; 48,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,57; -15,93</t>
+          <t>-44,41; -16,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 45,97</t>
+          <t>-6,39; 43,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,05</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 8,7</t>
+          <t>-5,67; 6,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,36</t>
+          <t>-10,21; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,85</t>
+          <t>-4,11; 25,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 6,89</t>
+          <t>-2,42; 8,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 0,4</t>
+          <t>-6,12; 3,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 26,0</t>
+          <t>-2,08; 9,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,89</t>
+          <t>-2,69; 5,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,02</t>
+          <t>-6,39; 1,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 20,32</t>
+          <t>-0,66; 14,89</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-41,93%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43,04%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>43,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-13,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-41,93%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 192,24</t>
+          <t>-40,82; 75,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 96,48</t>
+          <t>-70,97; 11,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 206,32</t>
+          <t>-33,18; 306,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 76,7</t>
+          <t>-28,12; 196,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,29; 9,33</t>
+          <t>-65,27; 88,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 265,63</t>
+          <t>-25,38; 189,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 77,36</t>
+          <t>-23,18; 82,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 16,73</t>
+          <t>-57,03; 15,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 264,41</t>
+          <t>-10,24; 189,66</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,45</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,44</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-1,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,04</t>
+          <t>-4,67; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,88</t>
+          <t>-9,31; 0,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 12,7</t>
+          <t>-8,28; 1,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 5,3</t>
+          <t>0,91; 10,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 0,63</t>
+          <t>-2,72; 5,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,89</t>
+          <t>-3,75; 5,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 6,6</t>
+          <t>-0,63; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,9</t>
+          <t>-4,95; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,82</t>
+          <t>-4,77; 2,07</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-33,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-25,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>67,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,18%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,33%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,42%</t>
+          <t>-13,03%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 160,47</t>
+          <t>-30,06; 62,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 97,88</t>
+          <t>-57,97; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 197,87</t>
+          <t>-51,62; 19,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 46,08</t>
+          <t>7,3; 178,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 9,17</t>
+          <t>-27,35; 96,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 21,2</t>
+          <t>-39,31; 94,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 73,46</t>
+          <t>-4,9; 78,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 21,79</t>
+          <t>-40,05; 19,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 52,94</t>
+          <t>-37,55; 23,04</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,27</t>
+          <t>-0,95; 11,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,5</t>
+          <t>-9,82; -0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 6,71</t>
+          <t>-4,39; 8,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 10,75</t>
+          <t>2,08; 12,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -0,22</t>
+          <t>-3,62; 4,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 8,33</t>
+          <t>-0,97; 9,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,26</t>
+          <t>1,97; 9,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,95</t>
+          <t>-5,46; 1,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,64</t>
+          <t>-1,39; 6,63</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-46,71%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>123,97%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34,35%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>47,87%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-46,71%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,7; 341,64</t>
+          <t>-9,52; 161,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 127,07</t>
+          <t>-73,32; -2,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 173,91</t>
+          <t>-37,71; 101,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 144,79</t>
+          <t>23,04; 343,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,09; 4,04</t>
+          <t>-47,86; 131,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 95,95</t>
+          <t>-13,11; 276,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,63; 160,15</t>
+          <t>21,03; 164,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 15,36</t>
+          <t>-55,73; 23,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 87,3</t>
+          <t>-13,51; 112,57</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-5,94</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 4,6</t>
+          <t>-2,77; 7,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; -1,52</t>
+          <t>-8,66; -0,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 3,9</t>
+          <t>-1,15; 10,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,86</t>
+          <t>-5,94; 4,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -0,13</t>
+          <t>-11,0; -1,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 11,01</t>
+          <t>-6,78; 3,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,03</t>
+          <t>-3,36; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -2,2</t>
+          <t>-8,56; -2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,02</t>
+          <t>-2,71; 5,48</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,77%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>38,03%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-7,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-54,22%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-14,76%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-42,77%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>-14,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 53,08</t>
+          <t>-21,45; 98,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,96; -15,47</t>
+          <t>-67,56; 2,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 45,55</t>
+          <t>-10,61; 125,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 95,68</t>
+          <t>-45,37; 47,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 1,98</t>
+          <t>-75,72; -16,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 131,96</t>
+          <t>-50,66; 43,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 56,63</t>
+          <t>-26,4; 46,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,54; -24,4</t>
+          <t>-65,83; -23,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 66,38</t>
+          <t>-21,29; 61,52</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,03</t>
+          <t>-0,72; 4,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,94</t>
+          <t>-7,22; -2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,81</t>
+          <t>-2,02; 5,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,95</t>
+          <t>0,79; 5,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -2,1</t>
+          <t>-3,9; 0,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,36</t>
+          <t>-1,33; 3,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,45</t>
+          <t>1,01; 4,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -1,5</t>
+          <t>-4,78; -1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,24</t>
+          <t>-1,17; 3,5</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-40,01%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-17,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-40,01%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,76; 87,89</t>
+          <t>-6,27; 46,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 14,23</t>
+          <t>-55,47; -21,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 67,04</t>
+          <t>-16,67; 52,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 47,31</t>
+          <t>7,67; 84,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -20,42</t>
+          <t>-40,67; 10,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 61,31</t>
+          <t>-15,43; 55,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14; 48,39</t>
+          <t>9,16; 50,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -16,04</t>
+          <t>-43,99; -16,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 43,93</t>
+          <t>-11,15; 37,9</t>
         </is>
       </c>
     </row>
